--- a/Статистика работы механизмов/Список обработок без статистики.xlsx
+++ b/Статистика работы механизмов/Список обработок без статистики.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="284">
   <si>
     <t>Отчеты:</t>
   </si>
@@ -864,6 +864,9 @@
   </si>
   <si>
     <t>нет в спраовчнике</t>
+  </si>
+  <si>
+    <t>Не_Используется</t>
   </si>
 </sst>
 </file>
@@ -1812,6 +1815,9 @@
       <c r="B11" t="s">
         <v>88</v>
       </c>
+      <c r="C11" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1820,6 +1826,9 @@
       <c r="B12" t="s">
         <v>89</v>
       </c>
+      <c r="C12" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1828,6 +1837,9 @@
       <c r="B13" t="s">
         <v>90</v>
       </c>
+      <c r="C13" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1836,6 +1848,9 @@
       <c r="B14" t="s">
         <v>91</v>
       </c>
+      <c r="C14" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -1844,6 +1859,9 @@
       <c r="B15" t="s">
         <v>92</v>
       </c>
+      <c r="C15" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -1852,6 +1870,9 @@
       <c r="B16" t="s">
         <v>93</v>
       </c>
+      <c r="C16" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -1860,6 +1881,9 @@
       <c r="B17" t="s">
         <v>94</v>
       </c>
+      <c r="C17" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -2129,6 +2153,9 @@
       <c r="B42" t="s">
         <v>119</v>
       </c>
+      <c r="C42" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -2137,6 +2164,9 @@
       <c r="B43" t="s">
         <v>120</v>
       </c>
+      <c r="C43" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -2145,6 +2175,9 @@
       <c r="B44" t="s">
         <v>121</v>
       </c>
+      <c r="C44" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
@@ -2153,6 +2186,9 @@
       <c r="B45" t="s">
         <v>122</v>
       </c>
+      <c r="C45" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
@@ -2161,6 +2197,9 @@
       <c r="B46" t="s">
         <v>123</v>
       </c>
+      <c r="C46" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
@@ -2169,6 +2208,9 @@
       <c r="B47" t="s">
         <v>124</v>
       </c>
+      <c r="C47" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -2177,6 +2219,9 @@
       <c r="B48" t="s">
         <v>125</v>
       </c>
+      <c r="C48" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -2185,6 +2230,9 @@
       <c r="B49" t="s">
         <v>126</v>
       </c>
+      <c r="C49" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -2204,6 +2252,9 @@
       <c r="B51" t="s">
         <v>128</v>
       </c>
+      <c r="C51" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
@@ -2212,6 +2263,9 @@
       <c r="B52" t="s">
         <v>129</v>
       </c>
+      <c r="C52" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -2220,6 +2274,9 @@
       <c r="B53" t="s">
         <v>130</v>
       </c>
+      <c r="C53" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -2228,6 +2285,9 @@
       <c r="B54" t="s">
         <v>131</v>
       </c>
+      <c r="C54" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
@@ -2247,6 +2307,9 @@
       <c r="B56" t="s">
         <v>133</v>
       </c>
+      <c r="C56" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
@@ -2255,6 +2318,9 @@
       <c r="B57" t="s">
         <v>134</v>
       </c>
+      <c r="C57" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -2263,6 +2329,9 @@
       <c r="B58" t="s">
         <v>135</v>
       </c>
+      <c r="C58" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
@@ -2271,6 +2340,9 @@
       <c r="B59" t="s">
         <v>136</v>
       </c>
+      <c r="C59" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
@@ -2279,6 +2351,9 @@
       <c r="B60" t="s">
         <v>137</v>
       </c>
+      <c r="C60" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
@@ -2287,6 +2362,9 @@
       <c r="B61" t="s">
         <v>138</v>
       </c>
+      <c r="C61" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
@@ -2295,6 +2373,9 @@
       <c r="B62" t="s">
         <v>139</v>
       </c>
+      <c r="C62" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
@@ -2303,6 +2384,9 @@
       <c r="B63" t="s">
         <v>140</v>
       </c>
+      <c r="C63" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
@@ -2311,6 +2395,9 @@
       <c r="B64" t="s">
         <v>141</v>
       </c>
+      <c r="C64" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
@@ -2330,6 +2417,9 @@
       <c r="B66" t="s">
         <v>143</v>
       </c>
+      <c r="C66" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
@@ -2338,6 +2428,9 @@
       <c r="B67" t="s">
         <v>144</v>
       </c>
+      <c r="C67" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
@@ -2346,6 +2439,9 @@
       <c r="B68" t="s">
         <v>145</v>
       </c>
+      <c r="C68" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -2354,6 +2450,9 @@
       <c r="B69" t="s">
         <v>146</v>
       </c>
+      <c r="C69" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -2362,6 +2461,9 @@
       <c r="B70" t="s">
         <v>147</v>
       </c>
+      <c r="C70" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
@@ -2370,6 +2472,9 @@
       <c r="B71" t="s">
         <v>148</v>
       </c>
+      <c r="C71" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
@@ -2378,6 +2483,9 @@
       <c r="B72" t="s">
         <v>149</v>
       </c>
+      <c r="C72" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
@@ -2386,6 +2494,9 @@
       <c r="B73" t="s">
         <v>150</v>
       </c>
+      <c r="C73" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
@@ -2394,6 +2505,9 @@
       <c r="B74" t="s">
         <v>151</v>
       </c>
+      <c r="C74" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
@@ -2424,6 +2538,9 @@
       <c r="B77" t="s">
         <v>154</v>
       </c>
+      <c r="C77" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
@@ -2432,6 +2549,9 @@
       <c r="B78" t="s">
         <v>155</v>
       </c>
+      <c r="C78" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
@@ -2440,6 +2560,9 @@
       <c r="B79" t="s">
         <v>156</v>
       </c>
+      <c r="C79" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
@@ -2448,6 +2571,9 @@
       <c r="B80" t="s">
         <v>157</v>
       </c>
+      <c r="C80" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
@@ -2467,6 +2593,9 @@
       <c r="B82" t="s">
         <v>159</v>
       </c>
+      <c r="C82" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
@@ -2475,6 +2604,9 @@
       <c r="B83" t="s">
         <v>160</v>
       </c>
+      <c r="C83" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
@@ -2483,6 +2615,9 @@
       <c r="B84" t="s">
         <v>161</v>
       </c>
+      <c r="C84" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
@@ -2491,6 +2626,9 @@
       <c r="B85" t="s">
         <v>162</v>
       </c>
+      <c r="C85" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
@@ -2510,6 +2648,9 @@
       <c r="B87" t="s">
         <v>164</v>
       </c>
+      <c r="C87" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
@@ -2529,6 +2670,9 @@
       <c r="B89" t="s">
         <v>166</v>
       </c>
+      <c r="C89" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
@@ -2537,6 +2681,9 @@
       <c r="B90" t="s">
         <v>167</v>
       </c>
+      <c r="C90" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
@@ -2545,6 +2692,9 @@
       <c r="B91" t="s">
         <v>168</v>
       </c>
+      <c r="C91" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
@@ -2553,6 +2703,9 @@
       <c r="B92" t="s">
         <v>169</v>
       </c>
+      <c r="C92" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
@@ -2561,6 +2714,9 @@
       <c r="B93" t="s">
         <v>170</v>
       </c>
+      <c r="C93" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
@@ -2569,6 +2725,9 @@
       <c r="B94" t="s">
         <v>171</v>
       </c>
+      <c r="C94" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
@@ -2577,6 +2736,9 @@
       <c r="B95" t="s">
         <v>172</v>
       </c>
+      <c r="C95" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
@@ -2585,95 +2747,110 @@
       <c r="B96" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C96" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>96</v>
       </c>
       <c r="B97" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C97" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>97</v>
       </c>
       <c r="B98" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C98" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>98</v>
       </c>
       <c r="B99" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C99" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>99</v>
       </c>
       <c r="B100" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C100" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>111</v>
       </c>

--- a/Статистика работы механизмов/Список обработок без статистики.xlsx
+++ b/Статистика работы механизмов/Список обработок без статистики.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="153222"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13425"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13428"/>
   </bookViews>
   <sheets>
     <sheet name="Лист4" sheetId="4" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="283">
   <si>
     <t>Отчеты:</t>
   </si>
@@ -854,9 +854,6 @@
     <t>пометка на удаление</t>
   </si>
   <si>
-    <t>Добавить оповещение Обработка._ИмпортДанныхДляОтчетности</t>
-  </si>
-  <si>
     <t>да</t>
   </si>
   <si>
@@ -866,7 +863,7 @@
     <t>нет в спраовчнике</t>
   </si>
   <si>
-    <t>Не_Используется</t>
+    <t>__Не_Используется</t>
   </si>
 </sst>
 </file>
@@ -1033,7 +1030,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1213,6 +1210,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -1374,9 +1377,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% — акцент1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1699,12 +1703,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C178"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="81.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="81.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1712,7 +1716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1723,29 +1727,29 @@
         <v>276</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1756,7 +1760,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1767,7 +1771,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1778,18 +1782,18 @@
         <v>274</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1800,7 +1804,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1808,18 +1812,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1827,10 +1831,10 @@
         <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1841,92 +1845,95 @@
         <v>274</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C19" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C20" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C21" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C21" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1934,21 +1941,21 @@
         <v>99</v>
       </c>
       <c r="C22" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C23" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C23" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1959,7 +1966,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1970,18 +1977,18 @@
         <v>278</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C26" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C26" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -1992,7 +1999,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -2000,10 +2007,10 @@
         <v>105</v>
       </c>
       <c r="C28" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -2014,7 +2021,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -2022,10 +2029,10 @@
         <v>107</v>
       </c>
       <c r="C30" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -2033,10 +2040,10 @@
         <v>108</v>
       </c>
       <c r="C31" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -2044,10 +2051,10 @@
         <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -2055,10 +2062,10 @@
         <v>110</v>
       </c>
       <c r="C33" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -2066,10 +2073,10 @@
         <v>111</v>
       </c>
       <c r="C34" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -2080,7 +2087,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -2088,10 +2095,10 @@
         <v>113</v>
       </c>
       <c r="C36" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -2102,7 +2109,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -2110,10 +2117,10 @@
         <v>115</v>
       </c>
       <c r="C38" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -2121,10 +2128,10 @@
         <v>116</v>
       </c>
       <c r="C39" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -2132,10 +2139,10 @@
         <v>117</v>
       </c>
       <c r="C40" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -2143,10 +2150,10 @@
         <v>118</v>
       </c>
       <c r="C41" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -2154,10 +2161,10 @@
         <v>119</v>
       </c>
       <c r="C42" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -2165,10 +2172,10 @@
         <v>120</v>
       </c>
       <c r="C43" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -2176,10 +2183,10 @@
         <v>121</v>
       </c>
       <c r="C44" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -2187,10 +2194,10 @@
         <v>122</v>
       </c>
       <c r="C45" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>46</v>
       </c>
@@ -2198,10 +2205,10 @@
         <v>123</v>
       </c>
       <c r="C46" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -2209,10 +2216,10 @@
         <v>124</v>
       </c>
       <c r="C47" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -2220,10 +2227,10 @@
         <v>125</v>
       </c>
       <c r="C48" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -2231,10 +2238,10 @@
         <v>126</v>
       </c>
       <c r="C49" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -2242,10 +2249,10 @@
         <v>127</v>
       </c>
       <c r="C50" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -2253,10 +2260,10 @@
         <v>128</v>
       </c>
       <c r="C51" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -2264,10 +2271,10 @@
         <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -2275,10 +2282,10 @@
         <v>130</v>
       </c>
       <c r="C53" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>54</v>
       </c>
@@ -2286,10 +2293,10 @@
         <v>131</v>
       </c>
       <c r="C54" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>55</v>
       </c>
@@ -2297,10 +2304,10 @@
         <v>132</v>
       </c>
       <c r="C55" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>56</v>
       </c>
@@ -2308,10 +2315,10 @@
         <v>133</v>
       </c>
       <c r="C56" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>57</v>
       </c>
@@ -2319,10 +2326,10 @@
         <v>134</v>
       </c>
       <c r="C57" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -2330,10 +2337,10 @@
         <v>135</v>
       </c>
       <c r="C58" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>59</v>
       </c>
@@ -2341,10 +2348,10 @@
         <v>136</v>
       </c>
       <c r="C59" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>60</v>
       </c>
@@ -2352,10 +2359,10 @@
         <v>137</v>
       </c>
       <c r="C60" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>61</v>
       </c>
@@ -2363,10 +2370,10 @@
         <v>138</v>
       </c>
       <c r="C61" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>62</v>
       </c>
@@ -2374,10 +2381,10 @@
         <v>139</v>
       </c>
       <c r="C62" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>63</v>
       </c>
@@ -2385,10 +2392,10 @@
         <v>140</v>
       </c>
       <c r="C63" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>64</v>
       </c>
@@ -2396,10 +2403,10 @@
         <v>141</v>
       </c>
       <c r="C64" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>65</v>
       </c>
@@ -2407,10 +2414,10 @@
         <v>142</v>
       </c>
       <c r="C65" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>66</v>
       </c>
@@ -2418,10 +2425,10 @@
         <v>143</v>
       </c>
       <c r="C66" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>67</v>
       </c>
@@ -2429,10 +2436,10 @@
         <v>144</v>
       </c>
       <c r="C67" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>68</v>
       </c>
@@ -2440,10 +2447,10 @@
         <v>145</v>
       </c>
       <c r="C68" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>69</v>
       </c>
@@ -2451,10 +2458,10 @@
         <v>146</v>
       </c>
       <c r="C69" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>70</v>
       </c>
@@ -2462,10 +2469,10 @@
         <v>147</v>
       </c>
       <c r="C70" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>71</v>
       </c>
@@ -2473,10 +2480,10 @@
         <v>148</v>
       </c>
       <c r="C71" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>72</v>
       </c>
@@ -2484,10 +2491,10 @@
         <v>149</v>
       </c>
       <c r="C72" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -2495,10 +2502,10 @@
         <v>150</v>
       </c>
       <c r="C73" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>74</v>
       </c>
@@ -2506,10 +2513,10 @@
         <v>151</v>
       </c>
       <c r="C74" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>75</v>
       </c>
@@ -2517,10 +2524,10 @@
         <v>152</v>
       </c>
       <c r="C75" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>76</v>
       </c>
@@ -2531,7 +2538,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>77</v>
       </c>
@@ -2539,10 +2546,10 @@
         <v>154</v>
       </c>
       <c r="C77" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>78</v>
       </c>
@@ -2550,10 +2557,10 @@
         <v>155</v>
       </c>
       <c r="C78" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>79</v>
       </c>
@@ -2561,10 +2568,10 @@
         <v>156</v>
       </c>
       <c r="C79" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>80</v>
       </c>
@@ -2572,10 +2579,10 @@
         <v>157</v>
       </c>
       <c r="C80" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>81</v>
       </c>
@@ -2583,10 +2590,10 @@
         <v>158</v>
       </c>
       <c r="C81" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>82</v>
       </c>
@@ -2594,10 +2601,10 @@
         <v>159</v>
       </c>
       <c r="C82" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -2605,10 +2612,10 @@
         <v>160</v>
       </c>
       <c r="C83" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>84</v>
       </c>
@@ -2616,10 +2623,10 @@
         <v>161</v>
       </c>
       <c r="C84" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>85</v>
       </c>
@@ -2627,10 +2634,10 @@
         <v>162</v>
       </c>
       <c r="C85" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>86</v>
       </c>
@@ -2638,10 +2645,10 @@
         <v>163</v>
       </c>
       <c r="C86" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>87</v>
       </c>
@@ -2649,10 +2656,10 @@
         <v>164</v>
       </c>
       <c r="C87" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>1</v>
       </c>
@@ -2660,10 +2667,10 @@
         <v>165</v>
       </c>
       <c r="C88" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -2674,7 +2681,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -2682,10 +2689,10 @@
         <v>167</v>
       </c>
       <c r="C90" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -2693,10 +2700,10 @@
         <v>168</v>
       </c>
       <c r="C91" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -2704,10 +2711,10 @@
         <v>169</v>
       </c>
       <c r="C92" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -2715,10 +2722,10 @@
         <v>170</v>
       </c>
       <c r="C93" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -2726,10 +2733,10 @@
         <v>171</v>
       </c>
       <c r="C94" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -2737,10 +2744,10 @@
         <v>172</v>
       </c>
       <c r="C95" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -2748,10 +2755,10 @@
         <v>173</v>
       </c>
       <c r="C96" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -2759,10 +2766,10 @@
         <v>174</v>
       </c>
       <c r="C97" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -2770,10 +2777,10 @@
         <v>175</v>
       </c>
       <c r="C98" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -2781,10 +2788,10 @@
         <v>176</v>
       </c>
       <c r="C99" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>99</v>
       </c>
@@ -2792,395 +2799,395 @@
         <v>177</v>
       </c>
       <c r="C100" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>177</v>
       </c>
@@ -3194,487 +3201,487 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A96"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="132.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="132.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>273</v>
       </c>

--- a/Статистика работы механизмов/Список обработок без статистики.xlsx
+++ b/Статистика работы механизмов/Список обработок без статистики.xlsx
@@ -1722,10 +1722,10 @@
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="A45" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="2" t="s">
         <v>171</v>
       </c>
     </row>
